--- a/data/scaling_summary.xlsx
+++ b/data/scaling_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\pycharm_projects\network_simulations\thesis\throughput_upperbound\simulations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D43DF9-6F70-418B-97A3-F96E0F061CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2844C0D0-DECD-4872-A824-39EFFA029E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{721E2542-CFD3-F545-91FB-44EA0C7E0544}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{721E2542-CFD3-F545-91FB-44EA0C7E0544}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="326">
   <si>
     <t>source_id</t>
   </si>
@@ -550,9 +550,6 @@
     <t>BT22</t>
   </si>
   <si>
-    <t>NaN</t>
-  </si>
-  <si>
     <t>CL</t>
   </si>
   <si>
@@ -565,9 +562,6 @@
     <t>OESCL</t>
   </si>
   <si>
-    <t>average</t>
-  </si>
-  <si>
     <t>KSP-FF</t>
   </si>
   <si>
@@ -722,13 +716,413 @@
   </si>
   <si>
     <t>351.67468413269694</t>
+  </si>
+  <si>
+    <t>FF-KSP</t>
+  </si>
+  <si>
+    <t>418.5520617401566</t>
+  </si>
+  <si>
+    <t>396.68750301039944</t>
+  </si>
+  <si>
+    <t>387.5621923950242</t>
+  </si>
+  <si>
+    <t>379.31578312176765</t>
+  </si>
+  <si>
+    <t>903.1620030340802</t>
+  </si>
+  <si>
+    <t>861.2657365538173</t>
+  </si>
+  <si>
+    <t>843.2854071503465</t>
+  </si>
+  <si>
+    <t>1861.660379677708</t>
+  </si>
+  <si>
+    <t>1796.3305074407642</t>
+  </si>
+  <si>
+    <t>1740.385994515336</t>
+  </si>
+  <si>
+    <t>1691.356018579632</t>
+  </si>
+  <si>
+    <t>1647.6690619803455</t>
+  </si>
+  <si>
+    <t>2613.221742203794</t>
+  </si>
+  <si>
+    <t>2481.4027123685305</t>
+  </si>
+  <si>
+    <t>2377.875521431131</t>
+  </si>
+  <si>
+    <t>2291.7028320079994</t>
+  </si>
+  <si>
+    <t>2217.5866346510043</t>
+  </si>
+  <si>
+    <t>1395.996508996316</t>
+  </si>
+  <si>
+    <t>1355.5437027983814</t>
+  </si>
+  <si>
+    <t>1319.9414628724012</t>
+  </si>
+  <si>
+    <t>1288.1026460564785</t>
+  </si>
+  <si>
+    <t>343.3787417275663</t>
+  </si>
+  <si>
+    <t>309.9991718231708</t>
+  </si>
+  <si>
+    <t>286.53911098252536</t>
+  </si>
+  <si>
+    <t>268.4894291261339</t>
+  </si>
+  <si>
+    <t>253.8630787525721</t>
+  </si>
+  <si>
+    <t>770.2465043825191</t>
+  </si>
+  <si>
+    <t>642.8124596673571</t>
+  </si>
+  <si>
+    <t>601.9356617723802</t>
+  </si>
+  <si>
+    <t>568.7039906486006</t>
+  </si>
+  <si>
+    <t>1695.904729498366</t>
+  </si>
+  <si>
+    <t>1502.752810836963</t>
+  </si>
+  <si>
+    <t>1371.4241583503447</t>
+  </si>
+  <si>
+    <t>1272.5025192574371</t>
+  </si>
+  <si>
+    <t>1193.6393871859943</t>
+  </si>
+  <si>
+    <t>2364.0460444259415</t>
+  </si>
+  <si>
+    <t>2033.7356946382156</t>
+  </si>
+  <si>
+    <t>1825.1398606547173</t>
+  </si>
+  <si>
+    <t>1674.1668079468245</t>
+  </si>
+  <si>
+    <t>1556.9519902145755</t>
+  </si>
+  <si>
+    <t>1248.516561414494</t>
+  </si>
+  <si>
+    <t>1116.8050344478916</t>
+  </si>
+  <si>
+    <t>1025.8001140630497</t>
+  </si>
+  <si>
+    <t>956.4771193650532</t>
+  </si>
+  <si>
+    <t>900.7245883330869</t>
+  </si>
+  <si>
+    <t>209.74510896388426</t>
+  </si>
+  <si>
+    <t>202.53736463687267</t>
+  </si>
+  <si>
+    <t>190.95824528595114</t>
+  </si>
+  <si>
+    <t>186.15960476860135</t>
+  </si>
+  <si>
+    <t>473.88317507256244</t>
+  </si>
+  <si>
+    <t>458.17210110521955</t>
+  </si>
+  <si>
+    <t>444.60178940754133</t>
+  </si>
+  <si>
+    <t>432.6546651512743</t>
+  </si>
+  <si>
+    <t>421.9832040504191</t>
+  </si>
+  <si>
+    <t>1076.4538713068034</t>
+  </si>
+  <si>
+    <t>1033.547975397269</t>
+  </si>
+  <si>
+    <t>997.5429593517699</t>
+  </si>
+  <si>
+    <t>966.4788392419663</t>
+  </si>
+  <si>
+    <t>939.1472382771075</t>
+  </si>
+  <si>
+    <t>1583.4892211846566</t>
+  </si>
+  <si>
+    <t>1488.3000656547158</t>
+  </si>
+  <si>
+    <t>1416.3971268267182</t>
+  </si>
+  <si>
+    <t>1357.9861794420508</t>
+  </si>
+  <si>
+    <t>1308.6304870120127</t>
+  </si>
+  <si>
+    <t>792.3099517122213</t>
+  </si>
+  <si>
+    <t>763.4836916440069</t>
+  </si>
+  <si>
+    <t>739.0750893376774</t>
+  </si>
+  <si>
+    <t>717.8684007148948</t>
+  </si>
+  <si>
+    <t>699.1042646763337</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>band</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>FF-kSP</t>
+  </si>
+  <si>
+    <t>Band</t>
+  </si>
+  <si>
+    <t>Active channels (N_{\text{active}})</t>
+  </si>
+  <si>
+    <t>Denominator (N_{\text{active}}\cdot 48\text{ GHz})</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>16.512 THz</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>8.256 THz</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>7.200 THz</t>
+  </si>
+  <si>
+    <t>4.320 THz</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>5.856 THz</t>
+  </si>
+  <si>
+    <t>10.176 THz</t>
+  </si>
+  <si>
+    <t>17.376 THz</t>
+  </si>
+  <si>
+    <t>25.632 THz</t>
+  </si>
+  <si>
+    <t>42.144 THz</t>
+  </si>
+  <si>
+    <t>Throughput</t>
+  </si>
+  <si>
+    <t>occupied_bandwidth</t>
+  </si>
+  <si>
+    <t>Band-normalized throughput</t>
+  </si>
+  <si>
+    <t>normalized capacity per Hz</t>
+  </si>
+  <si>
+    <t>network-wide throughput density over available payload bandwidth</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Avg link distance (km)</t>
+  </si>
+  <si>
+    <r>
+      <t>|N|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nodes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>|E|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>edges</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ω</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>connectivity</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>h̄</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color rgb="FF73726C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>avg shortest path (km)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>δ</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <vertAlign val="subscript"/>
+        <sz val="9"/>
+        <color rgb="FF73726C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>diameter (km)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>λ₁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>algebraic connectivity</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -765,6 +1159,45 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF3D3D3A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF73726C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0F6E56"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF993C1D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <vertAlign val="subscript"/>
+      <sz val="9"/>
+      <color rgb="FF73726C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -788,7 +1221,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -806,6 +1239,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2093,8 +2547,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3490614F-7F9D-4042-A7FC-AB8715563534}">
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="17.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
@@ -2104,7 +2561,7 @@
         <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D1" t="s">
         <v>99</v>
@@ -2130,7 +2587,7 @@
         <v>0.2</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>95</v>
@@ -2156,7 +2613,7 @@
         <v>0.4</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>96</v>
@@ -2172,22 +2629,6 @@
       </c>
       <c r="H3" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="K3">
-        <f>(E2-D2)/D2</f>
-        <v>1.0893862872524356</v>
-      </c>
-      <c r="L3">
-        <f>(F2-D2)/D2</f>
-        <v>2.4129822908607856</v>
-      </c>
-      <c r="M3">
-        <f>(G2-D2)/D2</f>
-        <v>2.7975835431887925</v>
-      </c>
-      <c r="N3">
-        <f>(H2-D2)/D2</f>
-        <v>5.7712469472594794</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -2198,7 +2639,7 @@
         <v>0.6</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D4" s="5">
         <v>362.946214722815</v>
@@ -2214,43 +2655,6 @@
       </c>
       <c r="H4" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="K4">
-        <f>(E3-D3)/D3</f>
-        <v>1.089828799367704</v>
-      </c>
-      <c r="L4">
-        <f>(F3-D3)/D3</f>
-        <v>2.3991573069144638</v>
-      </c>
-      <c r="M4">
-        <f>(G3-D3)/D3</f>
-        <v>2.7777930205855625</v>
-      </c>
-      <c r="N4">
-        <f>(H3-D3)/D3</f>
-        <v>5.6203061932820102</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R4" t="s">
-        <v>99</v>
-      </c>
-      <c r="S4" t="s">
-        <v>4</v>
-      </c>
-      <c r="T4" t="s">
-        <v>5</v>
-      </c>
-      <c r="U4" t="s">
-        <v>6</v>
-      </c>
-      <c r="V4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -2261,7 +2665,7 @@
         <v>0.8</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>97</v>
@@ -2278,32 +2682,6 @@
       <c r="H5" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="K5">
-        <f>(E4-D4)/D4</f>
-        <v>1.0899874742600089</v>
-      </c>
-      <c r="L5">
-        <f>(F4-D4)/D4</f>
-        <v>2.3881929116094409</v>
-      </c>
-      <c r="M5">
-        <f>(G4-D4)/D4</f>
-        <v>2.7619536440605588</v>
-      </c>
-      <c r="N5">
-        <f>(H4-D4)/D4</f>
-        <v>5.5163340122390041</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5">
-        <v>0.2</v>
-      </c>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
       <c r="V5" s="6"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -2314,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>98</v>
@@ -2331,32 +2709,6 @@
       <c r="H6" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K6">
-        <f>(E5-D5)/D5</f>
-        <v>1.0899468592777022</v>
-      </c>
-      <c r="L6">
-        <f>(F5-D5)/D5</f>
-        <v>2.379063526796938</v>
-      </c>
-      <c r="M6">
-        <f>(G5-D5)/D5</f>
-        <v>2.7486888483024101</v>
-      </c>
-      <c r="N6">
-        <f>(H5-D5)/D5</f>
-        <v>5.4369152149001874</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q6">
-        <v>0.4</v>
-      </c>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
       <c r="V6" s="6"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -2367,7 +2719,7 @@
         <v>0.2</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>117</v>
@@ -2384,32 +2736,6 @@
       <c r="H7" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="K7">
-        <f>(E6-D6)/D6</f>
-        <v>1.0897618446377551</v>
-      </c>
-      <c r="L7">
-        <f>(F6-D6)/D6</f>
-        <v>2.3712031906205686</v>
-      </c>
-      <c r="M7">
-        <f>(G6-D6)/D6</f>
-        <v>2.7372286329192059</v>
-      </c>
-      <c r="N7">
-        <f>(H6-D6)/D6</f>
-        <v>5.3726792041497839</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q7">
-        <v>0.6</v>
-      </c>
-      <c r="R7" s="5"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
       <c r="V7" s="6"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -2420,7 +2746,7 @@
         <v>0.4</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>118</v>
@@ -2437,32 +2763,6 @@
       <c r="H8" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="K8">
-        <f>(E7-D7)/D7</f>
-        <v>1.2580685498796076</v>
-      </c>
-      <c r="L8">
-        <f>(F7-D7)/D7</f>
-        <v>2.7540787117610148</v>
-      </c>
-      <c r="M8">
-        <f>(G7-D7)/D7</f>
-        <v>4.1810541469535547</v>
-      </c>
-      <c r="N8">
-        <f>(H7-D7)/D7</f>
-        <v>6.7133757167460439</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q8">
-        <v>0.8</v>
-      </c>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
       <c r="V8" s="6"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -2473,7 +2773,7 @@
         <v>0.6</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>119</v>
@@ -2490,32 +2790,6 @@
       <c r="H9" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="K9">
-        <f>(E8-D8)/D8</f>
-        <v>1.262237512733875</v>
-      </c>
-      <c r="L9">
-        <f>(F8-D8)/D8</f>
-        <v>2.7494022279398611</v>
-      </c>
-      <c r="M9">
-        <f>(G8-D8)/D8</f>
-        <v>4.1606101573956034</v>
-      </c>
-      <c r="N9">
-        <f>(H8-D8)/D8</f>
-        <v>6.5347699481178756</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
       <c r="V9" s="6"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -2526,7 +2800,7 @@
         <v>0.8</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>120</v>
@@ -2543,32 +2817,6 @@
       <c r="H10" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K10">
-        <f>(E9-D9)/D9</f>
-        <v>1.2653287710462882</v>
-      </c>
-      <c r="L10">
-        <f>(F9-D9)/D9</f>
-        <v>2.7459136145203127</v>
-      </c>
-      <c r="M10">
-        <f>(G9-D9)/D9</f>
-        <v>4.1443258775629186</v>
-      </c>
-      <c r="N10">
-        <f>(H9-D9)/D9</f>
-        <v>6.4164592252933987</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q10">
-        <v>0.2</v>
-      </c>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="6"/>
       <c r="V10" s="6"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -2579,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>121</v>
@@ -2596,32 +2844,6 @@
       <c r="H11" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K11">
-        <f>(E10-D10)/D10</f>
-        <v>1.2676626874699655</v>
-      </c>
-      <c r="L11">
-        <f>(F10-D10)/D10</f>
-        <v>2.742985378035399</v>
-      </c>
-      <c r="M11">
-        <f>(G10-D10)/D10</f>
-        <v>4.1305725820112622</v>
-      </c>
-      <c r="N11">
-        <f>(H10-D10)/D10</f>
-        <v>6.3279355109901454</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q11">
-        <v>0.4</v>
-      </c>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="6"/>
       <c r="V11" s="6"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -2632,7 +2854,7 @@
         <v>0.2</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>122</v>
@@ -2649,32 +2871,6 @@
       <c r="H12" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="K12">
-        <f>(E11-D11)/D11</f>
-        <v>1.269446783983041</v>
-      </c>
-      <c r="L12">
-        <f>(F11-D11)/D11</f>
-        <v>2.7403520131342924</v>
-      </c>
-      <c r="M12">
-        <f>(G11-D11)/D11</f>
-        <v>4.118519635618977</v>
-      </c>
-      <c r="N12">
-        <f>(H11-D11)/D11</f>
-        <v>6.2571978578622947</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q12">
-        <v>0.6</v>
-      </c>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
       <c r="V12" s="6"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -2685,7 +2881,7 @@
         <v>0.4</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>123</v>
@@ -2702,32 +2898,6 @@
       <c r="H13" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="K13">
-        <f>(E12-D12)/D12</f>
-        <v>1.2219508415988014</v>
-      </c>
-      <c r="L13">
-        <f>(F12-D12)/D12</f>
-        <v>2.5379138994597508</v>
-      </c>
-      <c r="M13">
-        <f>(G12-D12)/D12</f>
-        <v>3.8177286391911691</v>
-      </c>
-      <c r="N13">
-        <f>(H12-D12)/D12</f>
-        <v>5.712170699968123</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q13">
-        <v>0.8</v>
-      </c>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="6"/>
       <c r="V13" s="6"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -2738,7 +2908,7 @@
         <v>0.6</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>124</v>
@@ -2755,32 +2925,6 @@
       <c r="H14" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="K14">
-        <f>(E13-D13)/D13</f>
-        <v>1.2242720593321088</v>
-      </c>
-      <c r="L14">
-        <f>(F13-D13)/D13</f>
-        <v>2.5094861339334003</v>
-      </c>
-      <c r="M14">
-        <f>(G13-D13)/D13</f>
-        <v>3.7472708589528034</v>
-      </c>
-      <c r="N14">
-        <f>(H13-D13)/D13</f>
-        <v>5.4622153229040791</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
       <c r="V14" s="6"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -2791,7 +2935,7 @@
         <v>0.8</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>125</v>
@@ -2808,32 +2952,6 @@
       <c r="H15" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="K15">
-        <f>(E14-D14)/D14</f>
-        <v>1.2241334209813939</v>
-      </c>
-      <c r="L15">
-        <f>(F14-D14)/D14</f>
-        <v>2.4893055852258295</v>
-      </c>
-      <c r="M15">
-        <f>(G14-D14)/D14</f>
-        <v>3.6988984830845699</v>
-      </c>
-      <c r="N15">
-        <f>(H14-D14)/D14</f>
-        <v>5.3118063833237512</v>
-      </c>
-      <c r="P15" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q15">
-        <v>0.2</v>
-      </c>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
       <c r="V15" s="6"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -2844,7 +2962,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>126</v>
@@ -2860,28 +2978,6 @@
       </c>
       <c r="H16" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="K16">
-        <f>(E15-D15)/D15</f>
-        <v>1.2230371926792833</v>
-      </c>
-      <c r="L16">
-        <f>(F15-D15)/D15</f>
-        <v>2.4731987658874539</v>
-      </c>
-      <c r="M16">
-        <f>(G15-D15)/D15</f>
-        <v>3.6615240285595134</v>
-      </c>
-      <c r="N16">
-        <f>(H15-D15)/D15</f>
-        <v>5.2043780852881438</v>
-      </c>
-      <c r="P16" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q16">
-        <v>0.4</v>
       </c>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
@@ -2897,44 +2993,38 @@
         <v>0.2</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K17">
-        <f>(E16-D16)/D16</f>
-        <v>1.221516098332337</v>
+        <f>(E17-D17)/D17</f>
+        <v>1.1676910339174171</v>
       </c>
       <c r="L17">
-        <f t="shared" ref="L17:L25" si="0">(F16-D16)/D16</f>
-        <v>2.4596914869869053</v>
+        <f t="shared" ref="L17:L23" si="0">(F17-D17)/D17</f>
+        <v>2.6346058140562336</v>
       </c>
       <c r="M17">
-        <f t="shared" ref="M17:M25" si="1">(G16-D16)/D16</f>
-        <v>3.6310285913805731</v>
+        <f t="shared" ref="M17:M23" si="1">(G17-D17)/D17</f>
+        <v>3.9484161061386147</v>
       </c>
       <c r="N17">
-        <f t="shared" ref="N17:N25" si="2">(H16-D16)/D16</f>
-        <v>5.121250521519527</v>
-      </c>
-      <c r="P17" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q17">
-        <v>0.6</v>
+        <f t="shared" ref="N17:N23" si="2">(H17-D17)/D17</f>
+        <v>6.3597334546839148</v>
       </c>
       <c r="R17" s="6"/>
       <c r="S17" s="5"/>
@@ -2950,44 +3040,38 @@
         <v>0.4</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K18">
-        <f>(S20-R20)/R20</f>
-        <v>1.2194930590600215</v>
+        <f t="shared" ref="K17:K23" si="3">(E18-D18)/D18</f>
+        <v>1.1697076945185241</v>
       </c>
       <c r="L18">
-        <f>(T20-R20)/R20</f>
-        <v>2.6163887501461947</v>
+        <f t="shared" si="0"/>
+        <v>2.6270740981445844</v>
       </c>
       <c r="M18">
-        <f>(U20-R20)/R20</f>
-        <v>3.9447485200384946</v>
+        <f t="shared" si="1"/>
+        <v>3.9262733930638372</v>
       </c>
       <c r="N18">
-        <f>(V20-R20)/R20</f>
-        <v>6.3111371575731656</v>
-      </c>
-      <c r="P18" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q18">
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>6.2035503358247981</v>
       </c>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
@@ -3003,44 +3087,38 @@
         <v>0.6</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K19">
-        <f>(S21-R21)/R21</f>
-        <v>1.2183583937441955</v>
+        <f t="shared" si="3"/>
+        <v>1.1712311619795677</v>
       </c>
       <c r="L19">
-        <f>(T21-R21)/R21</f>
-        <v>2.6023032090817306</v>
+        <f t="shared" si="0"/>
+        <v>2.6207070117707891</v>
       </c>
       <c r="M19">
-        <f>(U21-R21)/R21</f>
-        <v>3.9147668458761822</v>
+        <f t="shared" si="1"/>
+        <v>3.9075342050849802</v>
       </c>
       <c r="N19">
-        <f>(V21-R21)/R21</f>
-        <v>6.1225976986898756</v>
-      </c>
-      <c r="P19" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>6.0932273083753916</v>
       </c>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
@@ -3056,60 +3134,44 @@
         <v>0.8</v>
       </c>
       <c r="C20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K20">
-        <f>(S22-R22)/R22</f>
-        <v>1.2173295792878487</v>
+        <f t="shared" si="3"/>
+        <v>1.1723997209815986</v>
       </c>
       <c r="L20">
-        <f>(T22-R22)/R22</f>
-        <v>2.5904305594649473</v>
+        <f t="shared" si="0"/>
+        <v>2.6151527371840362</v>
       </c>
       <c r="M20">
-        <f>(U22-R22)/R22</f>
-        <v>3.8891727176051476</v>
+        <f t="shared" si="1"/>
+        <v>3.8912234811208797</v>
       </c>
       <c r="N20">
-        <f>(V22-R22)/R22</f>
-        <v>5.988214480012279</v>
-      </c>
-      <c r="P20" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q20">
-        <v>0.2</v>
-      </c>
-      <c r="R20" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="S20" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="T20" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="U20" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="V20" s="6" t="s">
-        <v>194</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>6.0076969261547815</v>
+      </c>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -3119,60 +3181,44 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K21">
-        <f>(S23-R23)/R23</f>
-        <v>1.2163613852238118</v>
+        <f t="shared" si="3"/>
+        <v>1.1733014001491069</v>
       </c>
       <c r="L21">
-        <f>(T23-R23)/R23</f>
-        <v>2.5801456252908754</v>
+        <f t="shared" si="0"/>
+        <v>2.6101963266296737</v>
       </c>
       <c r="M21">
-        <f>(U23-R23)/R23</f>
-        <v>3.8667955419123916</v>
+        <f t="shared" si="1"/>
+        <v>3.8767356275364899</v>
       </c>
       <c r="N21">
-        <f>(V23-R23)/R23</f>
-        <v>5.8836791478574906</v>
-      </c>
-      <c r="P21" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q21">
-        <v>0.4</v>
-      </c>
-      <c r="R21" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="S21" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="T21" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="U21" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="V21" s="6" t="s">
-        <v>195</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>5.9378409269760697</v>
+      </c>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -3181,6 +3227,9 @@
       <c r="B22">
         <v>1</v>
       </c>
+      <c r="C22" t="s">
+        <v>170</v>
+      </c>
       <c r="D22">
         <v>432.41559999999998</v>
       </c>
@@ -3197,160 +3246,938 @@
         <v>3317.6731</v>
       </c>
       <c r="K22">
-        <f>(S24-R24)/R24</f>
-        <v>1.2154310974795155</v>
+        <f t="shared" si="3"/>
+        <v>1.1957508008499234</v>
       </c>
       <c r="L22">
-        <f>(T24-R24)/R24</f>
-        <v>2.5710519255924305</v>
-      </c>
-      <c r="M22">
-        <f>(U24-R24)/R24</f>
-        <v>3.846878301804602</v>
-      </c>
-      <c r="N22">
-        <f>(V24-R24)/R24</f>
-        <v>5.7982120058095568</v>
-      </c>
-      <c r="P22" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q22">
-        <v>0.6</v>
-      </c>
-      <c r="R22" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="S22" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="T22" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="U22" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="V22" s="6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="K23">
-        <f t="shared" ref="K18:K25" si="3">(E22-D22)/D22</f>
-        <v>1.1957508008499234</v>
-      </c>
-      <c r="L23">
         <f t="shared" si="0"/>
         <v>2.6453340258769571</v>
       </c>
-      <c r="M23">
+      <c r="M22">
         <f t="shared" si="1"/>
         <v>4.0712275412820444</v>
       </c>
-      <c r="N23">
+      <c r="N22">
         <f t="shared" si="2"/>
         <v>6.6724176926086853</v>
       </c>
-      <c r="P23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q23">
-        <v>0.8</v>
-      </c>
-      <c r="R23" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="S23" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="T23" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="U23" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="V23" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="K24" t="e">
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="K23" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L24" t="e">
+      <c r="L23" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M24" t="e">
+      <c r="M23" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N24" t="e">
+      <c r="N23" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P24" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q24">
-        <v>1</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="S24" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="T24" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="U24" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="V24" s="6" t="s">
-        <v>198</v>
-      </c>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24">
+        <v>0.2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>222</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E24" s="5">
+        <v>928.15408074553397</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1443.00442429391</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="K24">
+        <f>(E24-D24)/D24</f>
+        <v>1.2175355602996583</v>
+      </c>
+      <c r="L24">
+        <f>(F24-D24)/D24</f>
+        <v>2.4476103600936292</v>
+      </c>
+      <c r="M24">
+        <f>(G24-D24)/D24</f>
+        <v>3.4478585816486778</v>
+      </c>
+      <c r="N24">
+        <f>(H24-D24)/D24</f>
+        <v>5.2434807544350868</v>
+      </c>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
       <c r="Y24">
         <v>3090.5210999999999</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="K25" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L25" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M25" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N25" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="A25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25">
+        <v>0.4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D25" s="5">
+        <v>406.91094396588102</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K25">
+        <f t="shared" ref="K25:K44" si="4">(E25-D25)/D25</f>
+        <v>1.2195569237621908</v>
+      </c>
+      <c r="L25">
+        <f>(F25-D25)/D25</f>
+        <v>2.4307175309429936</v>
+      </c>
+      <c r="M25">
+        <f>(G25-D25)/D25</f>
+        <v>3.4145544229731506</v>
+      </c>
+      <c r="N25">
+        <f>(H25-D25)/D25</f>
+        <v>5.0981469020813375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26">
+        <v>0.6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>222</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="5">
+        <v>881.07790633942102</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="4"/>
+        <v>1.2210881352527103</v>
+      </c>
+      <c r="L26">
+        <f t="shared" ref="L26:L44" si="5">(F26-D26)/D26</f>
+        <v>2.4171575673833239</v>
+      </c>
+      <c r="M26">
+        <f t="shared" ref="M26:M44" si="6">(G26-D26)/D26</f>
+        <v>3.387297258693089</v>
+      </c>
+      <c r="N26">
+        <f t="shared" ref="N26:N44" si="7">(H26-D26)/D26</f>
+        <v>4.9943292979632758</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="P27" t="s">
+      <c r="A27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27">
+        <v>0.8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>222</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="4"/>
+        <v>1.22226458992669</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="5"/>
+        <v>2.4057539377500619</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="6"/>
+        <v>3.364089304293413</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="7"/>
+        <v>4.9131227890056017</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>222</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="4"/>
+        <v>1.2231751081120623</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="5"/>
+        <v>2.3958582884566297</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="6"/>
+        <v>3.3437925214185178</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="7"/>
+        <v>4.8462809440732286</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29">
+        <v>0.2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>222</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="4"/>
+        <v>1.2593288463959362</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="5"/>
+        <v>2.777489523479896</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="6"/>
+        <v>4.1322001100495482</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="7"/>
+        <v>6.5495883027113209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30">
+        <v>0.4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>222</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="4"/>
+        <v>1.2621608705468885</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="5"/>
+        <v>2.7695942820864246</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="6"/>
+        <v>4.1029990305754289</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="7"/>
+        <v>6.3482740743816519</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31">
+        <v>0.6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>222</v>
+      </c>
+      <c r="D31" s="5">
+        <v>196.36046184629399</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="4"/>
+        <v>1.2642123838329737</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="5"/>
+        <v>2.7638691740102259</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="6"/>
+        <v>4.0801620141463122</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="7"/>
+        <v>6.2132501294248845</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32">
+        <v>0.8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>222</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="4"/>
+        <v>1.2657029786977461</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="5"/>
+        <v>2.7592951256957767</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="6"/>
+        <v>4.0612050702220763</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="7"/>
+        <v>6.111429922329509</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>222</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="4"/>
+        <v>1.2667818003532505</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="5"/>
+        <v>2.7554026049063074</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="6"/>
+        <v>4.0448497645043888</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="7"/>
+        <v>6.0296157355869768</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34">
+        <v>0.2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="4"/>
+        <v>1.2431397485684379</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="5"/>
+        <v>2.6359751192898635</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="6"/>
+        <v>3.9388751352693738</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="7"/>
+        <v>5.8846604554849105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35">
+        <v>0.4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>222</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E35" s="5">
+        <v>695.67117674808503</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="4"/>
+        <v>1.2441065653714405</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="5"/>
+        <v>2.6026065098165452</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="6"/>
+        <v>3.8476026629327951</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="7"/>
+        <v>5.560455251145946</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36">
+        <v>0.6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>222</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="4"/>
+        <v>1.2433672578350388</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="5"/>
+        <v>2.5799654383851278</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="6"/>
+        <v>3.7861674228268898</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="7"/>
+        <v>5.3696011842726028</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
+        <v>0.8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>222</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="4"/>
+        <v>1.241934305315231</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="5"/>
+        <v>2.5624386497380942</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="6"/>
+        <v>3.7394883418654969</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="7"/>
+        <v>5.2355036226037681</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>222</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="4"/>
+        <v>1.2401996912788098</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="5"/>
+        <v>2.5480724206097665</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="6"/>
+        <v>3.7019022736637193</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="7"/>
+        <v>5.1330383207557944</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39">
+        <v>0.2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>222</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="4"/>
+        <v>1.2194930590600215</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="5"/>
+        <v>2.6163887501461947</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="6"/>
+        <v>3.9447485200384946</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="7"/>
+        <v>6.3111371575731656</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40">
+        <v>0.4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="4"/>
+        <v>1.2183583937441955</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="5"/>
+        <v>2.6023032090817306</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="6"/>
+        <v>3.9147668458761822</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="7"/>
+        <v>6.1225976986898756</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>165</v>
+      </c>
+      <c r="B41">
+        <v>0.6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>222</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="4"/>
+        <v>1.2173295792878487</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="5"/>
+        <v>2.5904305594649473</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="6"/>
+        <v>3.8891727176051476</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="7"/>
+        <v>5.988214480012279</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42">
+        <v>0.8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>222</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="4"/>
+        <v>1.2163613852238118</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="5"/>
+        <v>2.5801456252908754</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="6"/>
+        <v>3.8667955419123916</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="7"/>
+        <v>5.8836791478574906</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>222</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="4"/>
+        <v>1.2154310974795155</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="5"/>
+        <v>2.5710519255924305</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="6"/>
+        <v>3.846878301804602</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="7"/>
+        <v>5.7982120058095568</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>164</v>
       </c>
-      <c r="Q27">
+      <c r="B44">
         <v>1</v>
       </c>
-      <c r="S27">
+      <c r="C44" t="s">
+        <v>222</v>
+      </c>
+      <c r="D44">
+        <v>388.02140000000003</v>
+      </c>
+      <c r="E44">
         <v>876.76229999999998</v>
       </c>
-      <c r="T27">
+      <c r="F44">
         <v>1459.4879000000001</v>
       </c>
-      <c r="U27">
+      <c r="G44">
         <v>2022.8336999999999</v>
       </c>
-      <c r="V27">
+      <c r="H44">
         <v>3090.5210999999999</v>
+      </c>
+      <c r="K44">
+        <f>(F44-E44)/E44</f>
+        <v>0.66463350442873759</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="5"/>
+        <v>2.7613592961625311</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="6"/>
+        <v>4.2132013852844192</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="7"/>
+        <v>6.9648212701670573</v>
       </c>
     </row>
   </sheetData>
@@ -3361,13 +4188,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A703450D-67A4-4FD0-8232-05B7A7B415AD}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -3375,376 +4202,988 @@
         <v>78</v>
       </c>
       <c r="C1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B2">
         <v>0.2</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2">
         <v>1.0893862872524356</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>2.4129822908607856</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>2.7975835431887925</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>5.7712469472594794</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B3">
         <v>0.4</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3">
         <v>1.089828799367704</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>2.3991573069144638</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>2.7777930205855625</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>5.6203061932820102</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B4">
         <v>0.6</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4">
         <v>1.0899874742600089</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>2.3881929116094409</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>2.7619536440605588</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>5.5163340122390041</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
         <v>0.8</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5">
         <v>1.0899468592777022</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>2.379063526796938</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>2.7486888483024101</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>5.4369152149001874</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6">
         <v>1.0897618446377551</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>2.3712031906205686</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>2.7372286329192059</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>5.3726792041497839</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B7">
         <v>0.2</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7">
         <v>1.2580685498796076</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>2.7540787117610148</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>4.1810541469535547</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>6.7133757167460439</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B8">
         <v>0.4</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8">
         <v>1.262237512733875</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>2.7494022279398611</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>4.1606101573956034</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>6.5347699481178756</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B9">
         <v>0.6</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9">
         <v>1.2653287710462882</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>2.7459136145203127</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>4.1443258775629186</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>6.4164592252933987</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B10">
         <v>0.8</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10">
         <v>1.2676626874699655</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>2.742985378035399</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>4.1305725820112622</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>6.3279355109901454</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11">
         <v>1.269446783983041</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>2.7403520131342924</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>4.118519635618977</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>6.2571978578622947</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
       <c r="B12">
         <v>0.2</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12">
         <v>1.2219508415988014</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>2.5379138994597508</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>3.8177286391911691</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>5.712170699968123</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
       <c r="B13">
         <v>0.4</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13">
         <v>1.2242720593321088</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>2.5094861339334003</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>3.7472708589528034</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>5.4622153229040791</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
       <c r="B14">
         <v>0.6</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14">
         <v>1.2241334209813939</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>2.4893055852258295</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>3.6988984830845699</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>5.3118063833237512</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
       <c r="B15">
         <v>0.8</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15">
         <v>1.2230371926792833</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>2.4731987658874539</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>3.6615240285595134</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>5.2043780852881438</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>3317.6731</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16">
         <v>1.221516098332337</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>2.4596914869869053</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>3.6310285913805731</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>5.121250521519527</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>165</v>
       </c>
       <c r="B17">
         <v>0.2</v>
       </c>
+      <c r="C17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17">
+        <v>1.1676910339174171</v>
+      </c>
+      <c r="E17">
+        <v>2.6346058140562336</v>
+      </c>
       <c r="F17">
-        <v>3317.6731</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3.9484161061386147</v>
+      </c>
+      <c r="G17">
+        <v>6.3597334546839148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>165</v>
       </c>
       <c r="B18">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18">
+        <v>1.1697076945185241</v>
+      </c>
+      <c r="E18">
+        <v>2.6270740981445844</v>
+      </c>
+      <c r="F18">
+        <v>3.9262733930638372</v>
+      </c>
+      <c r="G18">
+        <v>6.2035503358247981</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>165</v>
       </c>
       <c r="B19">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19">
+        <v>1.1712311619795677</v>
+      </c>
+      <c r="E19">
+        <v>2.6207070117707891</v>
+      </c>
+      <c r="F19">
+        <v>3.9075342050849802</v>
+      </c>
+      <c r="G19">
+        <v>6.0932273083753916</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>165</v>
       </c>
       <c r="B20">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20">
+        <v>1.1723997209815986</v>
+      </c>
+      <c r="E20">
+        <v>2.6151527371840362</v>
+      </c>
+      <c r="F20">
+        <v>3.8912234811208797</v>
+      </c>
+      <c r="G20">
+        <v>6.0076969261547815</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>165</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21">
+        <v>1.1733014001491069</v>
+      </c>
+      <c r="E21">
+        <v>2.6101963266296737</v>
+      </c>
+      <c r="F21">
+        <v>3.8767356275364899</v>
+      </c>
+      <c r="G21">
+        <v>5.9378409269760697</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>164</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
+      <c r="C22" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22">
+        <v>1.1957508008499234</v>
+      </c>
       <c r="E22">
-        <v>2192.8779</v>
+        <v>2.6453340258769571</v>
       </c>
       <c r="F22">
-        <v>3317.6731</v>
+        <v>4.0712275412820444</v>
+      </c>
+      <c r="G22">
+        <v>6.6724176926086853</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24">
+        <v>0.2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>222</v>
+      </c>
+      <c r="D24">
+        <v>1.2175355602996583</v>
+      </c>
+      <c r="E24">
+        <v>2.4476103600936292</v>
+      </c>
+      <c r="F24">
+        <v>3.4478585816486778</v>
+      </c>
+      <c r="G24">
+        <v>5.2434807544350868</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25">
+        <v>0.4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D25">
+        <v>1.2195569237621908</v>
+      </c>
+      <c r="E25">
+        <v>2.4307175309429936</v>
+      </c>
+      <c r="F25">
+        <v>3.4145544229731506</v>
+      </c>
+      <c r="G25">
+        <v>5.0981469020813375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26">
+        <v>0.6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>222</v>
+      </c>
+      <c r="D26">
+        <v>1.2210881352527103</v>
+      </c>
+      <c r="E26">
+        <v>2.4171575673833239</v>
+      </c>
+      <c r="F26">
+        <v>3.387297258693089</v>
+      </c>
+      <c r="G26">
+        <v>4.9943292979632758</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27">
+        <v>0.8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>222</v>
+      </c>
+      <c r="D27">
+        <v>1.22226458992669</v>
+      </c>
+      <c r="E27">
+        <v>2.4057539377500619</v>
+      </c>
+      <c r="F27">
+        <v>3.364089304293413</v>
+      </c>
+      <c r="G27">
+        <v>4.9131227890056017</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>222</v>
+      </c>
+      <c r="D28">
+        <v>1.2231751081120623</v>
+      </c>
+      <c r="E28">
+        <v>2.3958582884566297</v>
+      </c>
+      <c r="F28">
+        <v>3.3437925214185178</v>
+      </c>
+      <c r="G28">
+        <v>4.8462809440732286</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29">
+        <v>0.2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>222</v>
+      </c>
+      <c r="D29">
+        <v>1.2593288463959362</v>
+      </c>
+      <c r="E29">
+        <v>2.777489523479896</v>
+      </c>
+      <c r="F29">
+        <v>4.1322001100495482</v>
+      </c>
+      <c r="G29">
+        <v>6.5495883027113209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30">
+        <v>0.4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>222</v>
+      </c>
+      <c r="D30">
+        <v>1.2621608705468885</v>
+      </c>
+      <c r="E30">
+        <v>2.7695942820864246</v>
+      </c>
+      <c r="F30">
+        <v>4.1029990305754289</v>
+      </c>
+      <c r="G30">
+        <v>6.3482740743816519</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31">
+        <v>0.6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>222</v>
+      </c>
+      <c r="D31">
+        <v>1.2642123838329737</v>
+      </c>
+      <c r="E31">
+        <v>2.7638691740102259</v>
+      </c>
+      <c r="F31">
+        <v>4.0801620141463122</v>
+      </c>
+      <c r="G31">
+        <v>6.2132501294248845</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32">
+        <v>0.8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>222</v>
+      </c>
+      <c r="D32">
+        <v>1.2657029786977461</v>
+      </c>
+      <c r="E32">
+        <v>2.7592951256957767</v>
+      </c>
+      <c r="F32">
+        <v>4.0612050702220763</v>
+      </c>
+      <c r="G32">
+        <v>6.111429922329509</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>222</v>
+      </c>
+      <c r="D33">
+        <v>1.2667818003532505</v>
+      </c>
+      <c r="E33">
+        <v>2.7554026049063074</v>
+      </c>
+      <c r="F33">
+        <v>4.0448497645043888</v>
+      </c>
+      <c r="G33">
+        <v>6.0296157355869768</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34">
+        <v>0.2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D34">
+        <v>1.2431397485684379</v>
+      </c>
+      <c r="E34">
+        <v>2.6359751192898635</v>
+      </c>
+      <c r="F34">
+        <v>3.9388751352693738</v>
+      </c>
+      <c r="G34">
+        <v>5.8846604554849105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35">
+        <v>0.4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>222</v>
+      </c>
+      <c r="D35">
+        <v>1.2441065653714405</v>
+      </c>
+      <c r="E35">
+        <v>2.6026065098165452</v>
+      </c>
+      <c r="F35">
+        <v>3.8476026629327951</v>
+      </c>
+      <c r="G35">
+        <v>5.560455251145946</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36">
+        <v>0.6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>222</v>
+      </c>
+      <c r="D36">
+        <v>1.2433672578350388</v>
+      </c>
+      <c r="E36">
+        <v>2.5799654383851278</v>
+      </c>
+      <c r="F36">
+        <v>3.7861674228268898</v>
+      </c>
+      <c r="G36">
+        <v>5.3696011842726028</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
+        <v>0.8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>222</v>
+      </c>
+      <c r="D37">
+        <v>1.241934305315231</v>
+      </c>
+      <c r="E37">
+        <v>2.5624386497380942</v>
+      </c>
+      <c r="F37">
+        <v>3.7394883418654969</v>
+      </c>
+      <c r="G37">
+        <v>5.2355036226037681</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>222</v>
+      </c>
+      <c r="D38">
+        <v>1.2401996912788098</v>
+      </c>
+      <c r="E38">
+        <v>2.5480724206097665</v>
+      </c>
+      <c r="F38">
+        <v>3.7019022736637193</v>
+      </c>
+      <c r="G38">
+        <v>5.1330383207557944</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39">
+        <v>0.2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>222</v>
+      </c>
+      <c r="D39">
+        <v>1.2194930590600215</v>
+      </c>
+      <c r="E39">
+        <v>2.6163887501461947</v>
+      </c>
+      <c r="F39">
+        <v>3.9447485200384946</v>
+      </c>
+      <c r="G39">
+        <v>6.3111371575731656</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40">
+        <v>0.4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40">
+        <v>1.2183583937441955</v>
+      </c>
+      <c r="E40">
+        <v>2.6023032090817306</v>
+      </c>
+      <c r="F40">
+        <v>3.9147668458761822</v>
+      </c>
+      <c r="G40">
+        <v>6.1225976986898756</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>165</v>
+      </c>
+      <c r="B41">
+        <v>0.6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>222</v>
+      </c>
+      <c r="D41">
+        <v>1.2173295792878487</v>
+      </c>
+      <c r="E41">
+        <v>2.5904305594649473</v>
+      </c>
+      <c r="F41">
+        <v>3.8891727176051476</v>
+      </c>
+      <c r="G41">
+        <v>5.988214480012279</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42">
+        <v>0.8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>222</v>
+      </c>
+      <c r="D42">
+        <v>1.2163613852238118</v>
+      </c>
+      <c r="E42">
+        <v>2.5801456252908754</v>
+      </c>
+      <c r="F42">
+        <v>3.8667955419123916</v>
+      </c>
+      <c r="G42">
+        <v>5.8836791478574906</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>222</v>
+      </c>
+      <c r="D43">
+        <v>1.2154310974795155</v>
+      </c>
+      <c r="E43">
+        <v>2.5710519255924305</v>
+      </c>
+      <c r="F43">
+        <v>3.846878301804602</v>
+      </c>
+      <c r="G43">
+        <v>5.7982120058095568</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>164</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>222</v>
+      </c>
+      <c r="D44">
+        <v>0.66463350442873759</v>
+      </c>
+      <c r="E44">
+        <v>2.7613592961625311</v>
+      </c>
+      <c r="F44">
+        <v>4.2132013852844192</v>
+      </c>
+      <c r="G44">
+        <v>6.9648212701670573</v>
       </c>
     </row>
   </sheetData>
@@ -3754,394 +5193,1415 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD85AC6-E966-4E05-9E71-1EE87D51305D}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
+      <c r="B1" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>293</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="F1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="I2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="6"/>
+      <c r="B2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>0.01</v>
+      </c>
+      <c r="E2">
+        <v>0.120952</v>
+      </c>
+      <c r="F2">
+        <v>0.35</v>
+      </c>
+      <c r="I2" s="5"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="I3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>1.6948999999999999E-2</v>
+      </c>
+      <c r="E3">
+        <v>0.120056</v>
+      </c>
+      <c r="F3">
+        <v>0.67796599999999996</v>
+      </c>
+      <c r="I3" s="5"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6">
-        <v>0.120292</v>
-      </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="5"/>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>9.5919999999999998E-3</v>
+      </c>
+      <c r="E4">
+        <v>0.120132</v>
+      </c>
+      <c r="F4">
+        <v>0.81774599999999997</v>
+      </c>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6">
-        <v>0.120292</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="I5" t="s">
-        <v>165</v>
-      </c>
-      <c r="J5" s="6"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>6.9319999999999998E-3</v>
+      </c>
+      <c r="E5">
+        <v>0.120409</v>
+      </c>
+      <c r="F5">
+        <v>0.86828399999999994</v>
+      </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="I6" t="s">
-        <v>164</v>
-      </c>
-      <c r="J6" s="6"/>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>2.2729999999999998E-3</v>
+      </c>
+      <c r="E6">
+        <v>0.120292</v>
+      </c>
+      <c r="F6">
+        <v>0.92613599999999996</v>
+      </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="5"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="5"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="H14" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="C15" s="5" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0.2525</v>
+      </c>
+      <c r="F7">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0.25</v>
+      </c>
+      <c r="F8">
+        <v>0.97033899999999995</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0.13913</v>
+      </c>
+      <c r="N8">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0.251799</v>
+      </c>
+      <c r="F9">
+        <v>0.983213</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0.13467199999999999</v>
+      </c>
+      <c r="N9">
+        <v>0.92372900000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0.251083</v>
+      </c>
+      <c r="F10">
+        <v>0.98786799999999997</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0.13397999999999999</v>
+      </c>
+      <c r="N10">
+        <v>0.95683499999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0.24943199999999999</v>
+      </c>
+      <c r="F11">
+        <v>0.98636400000000002</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0.13375000000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.968804</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0.13913</v>
+      </c>
+      <c r="F12">
+        <v>0.82</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0.132905</v>
+      </c>
+      <c r="N12">
+        <v>0.97727299999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0.13467199999999999</v>
+      </c>
+      <c r="F13">
+        <v>0.92372900000000002</v>
+      </c>
+      <c r="L13">
+        <v>0.01</v>
+      </c>
+      <c r="M13">
+        <v>0.120952</v>
+      </c>
+      <c r="N13">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0.13397999999999999</v>
+      </c>
+      <c r="F14">
+        <v>0.95683499999999999</v>
+      </c>
+      <c r="L14">
+        <v>1.6948999999999999E-2</v>
+      </c>
+      <c r="M14">
+        <v>0.120056</v>
+      </c>
+      <c r="N14">
+        <v>0.67796599999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0.13375000000000001</v>
+      </c>
+      <c r="F15">
+        <v>0.968804</v>
+      </c>
+      <c r="L15">
+        <v>9.5919999999999998E-3</v>
+      </c>
+      <c r="M15">
+        <v>0.120132</v>
+      </c>
+      <c r="N15">
+        <v>0.81774599999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0.132905</v>
+      </c>
+      <c r="F16">
+        <v>0.97727299999999995</v>
+      </c>
+      <c r="L16">
+        <v>6.9319999999999998E-3</v>
+      </c>
+      <c r="M16">
+        <v>0.120409</v>
+      </c>
+      <c r="N16">
+        <v>0.86828399999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>0.01</v>
+      </c>
+      <c r="E17">
+        <v>0.120952</v>
+      </c>
+      <c r="F17">
+        <v>0.35</v>
+      </c>
+      <c r="L17">
+        <v>2.2729999999999998E-3</v>
+      </c>
+      <c r="M17">
+        <v>0.120292</v>
+      </c>
+      <c r="N17">
+        <v>0.92613599999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>1.6948999999999999E-2</v>
+      </c>
+      <c r="E18">
+        <v>0.120056</v>
+      </c>
+      <c r="F18">
+        <v>0.67796599999999996</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0.11457100000000001</v>
+      </c>
+      <c r="N18">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>9.5919999999999998E-3</v>
+      </c>
+      <c r="E19">
+        <v>0.120132</v>
+      </c>
+      <c r="F19">
+        <v>0.81774599999999997</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0.111622</v>
+      </c>
+      <c r="N19">
+        <v>0.82627099999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>6.9319999999999998E-3</v>
+      </c>
+      <c r="E20">
+        <v>0.120409</v>
+      </c>
+      <c r="F20">
+        <v>0.86828399999999994</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0.11086</v>
+      </c>
+      <c r="N20">
+        <v>0.90167900000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21">
+        <v>2.2729999999999998E-3</v>
+      </c>
+      <c r="E21">
+        <v>0.120292</v>
+      </c>
+      <c r="F21">
+        <v>0.92613599999999996</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0.110275</v>
+      </c>
+      <c r="N21">
+        <v>0.92894299999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0.11457100000000001</v>
+      </c>
+      <c r="F22">
+        <v>0.59</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0.10987</v>
+      </c>
+      <c r="N22">
+        <v>0.95113599999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0.111622</v>
+      </c>
+      <c r="F23">
+        <v>0.82627099999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0.11086</v>
+      </c>
+      <c r="F24">
+        <v>0.90167900000000001</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0.11913</v>
+      </c>
+      <c r="N24">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0.110275</v>
+      </c>
+      <c r="F25">
+        <v>0.92894299999999996</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0.117354</v>
+      </c>
+      <c r="N25">
+        <v>0.974576</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0.10987</v>
+      </c>
+      <c r="F26">
+        <v>0.95113599999999998</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0.11907</v>
+      </c>
+      <c r="N26">
+        <v>0.98561200000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0.119057</v>
+      </c>
+      <c r="N27">
+        <v>0.98960099999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="B28" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="6">
-        <v>100</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>0.120952</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="C28" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0.11913</v>
+      </c>
+      <c r="F28">
+        <v>0.94</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0.118824</v>
+      </c>
+      <c r="N28">
+        <v>0.99090900000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="J15">
+      <c r="C29" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0.117354</v>
+      </c>
+      <c r="F29">
+        <v>0.974576</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0.13869600000000001</v>
+      </c>
+      <c r="N29">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0.11907</v>
+      </c>
+      <c r="F30">
+        <v>0.98561200000000004</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0.13780400000000001</v>
+      </c>
+      <c r="N30">
+        <v>0.54661000000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0.119057</v>
+      </c>
+      <c r="F31">
+        <v>0.98960099999999995</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0.13658600000000001</v>
+      </c>
+      <c r="N31">
+        <v>0.546763</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0.118824</v>
+      </c>
+      <c r="F32">
+        <v>0.99090900000000004</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0.13608600000000001</v>
+      </c>
+      <c r="N32">
+        <v>0.54592700000000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0.13869600000000001</v>
+      </c>
+      <c r="F33">
+        <v>0.54</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0.13572100000000001</v>
+      </c>
+      <c r="N33">
+        <v>0.54318200000000005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0.13780400000000001</v>
+      </c>
+      <c r="F34">
+        <v>0.54661000000000004</v>
+      </c>
+      <c r="L34">
+        <v>0.09</v>
+      </c>
+      <c r="M34">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="N34">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0.13658600000000001</v>
+      </c>
+      <c r="F35">
+        <v>0.546763</v>
+      </c>
+      <c r="L35">
+        <v>0.10169499999999999</v>
+      </c>
+      <c r="M35">
+        <v>0.23622899999999999</v>
+      </c>
+      <c r="N35">
+        <v>0.67796599999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0.13608600000000001</v>
+      </c>
+      <c r="F36">
+        <v>0.54592700000000005</v>
+      </c>
+      <c r="L36">
+        <v>0.107914</v>
+      </c>
+      <c r="M36">
+        <v>0.236211</v>
+      </c>
+      <c r="N36">
+        <v>0.67146300000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>169</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0.13572100000000001</v>
+      </c>
+      <c r="F37">
+        <v>0.54318200000000005</v>
+      </c>
+      <c r="L37">
+        <v>0.109185</v>
+      </c>
+      <c r="M37">
+        <v>0.235485</v>
+      </c>
+      <c r="N37">
+        <v>0.66551099999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D38">
+        <v>0.09</v>
+      </c>
+      <c r="E38">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="F38">
+        <v>0.68</v>
+      </c>
+      <c r="L38">
+        <v>0.10909099999999999</v>
+      </c>
+      <c r="M38">
+        <v>0.23508499999999999</v>
+      </c>
+      <c r="N38">
+        <v>0.66477299999999995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D39">
+        <v>0.10169499999999999</v>
+      </c>
+      <c r="E39">
+        <v>0.23622899999999999</v>
+      </c>
+      <c r="F39">
+        <v>0.67796599999999996</v>
+      </c>
+      <c r="L39">
         <v>0.01</v>
       </c>
-      <c r="K15">
-        <v>0.35</v>
-      </c>
-      <c r="L15">
-        <v>12.095238</v>
-      </c>
-      <c r="M15" t="s">
+      <c r="M39">
+        <v>0.12523799999999999</v>
+      </c>
+      <c r="N39">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>167</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D40">
+        <v>0.107914</v>
+      </c>
+      <c r="E40">
+        <v>0.236211</v>
+      </c>
+      <c r="F40">
+        <v>0.67146300000000003</v>
+      </c>
+      <c r="L40">
+        <v>4.2370000000000003E-3</v>
+      </c>
+      <c r="M40">
+        <v>0.12711900000000001</v>
+      </c>
+      <c r="N40">
+        <v>0.37711899999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>168</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D41">
+        <v>0.109185</v>
+      </c>
+      <c r="E41">
+        <v>0.235485</v>
+      </c>
+      <c r="F41">
+        <v>0.66551099999999996</v>
+      </c>
+      <c r="L41">
+        <v>2.398E-3</v>
+      </c>
+      <c r="M41">
+        <v>0.126413</v>
+      </c>
+      <c r="N41">
+        <v>0.38369300000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D42">
+        <v>0.10909099999999999</v>
+      </c>
+      <c r="E42">
+        <v>0.23508499999999999</v>
+      </c>
+      <c r="F42">
+        <v>0.66477299999999995</v>
+      </c>
+      <c r="L42">
+        <v>1.7329999999999999E-3</v>
+      </c>
+      <c r="M42">
+        <v>0.12742400000000001</v>
+      </c>
+      <c r="N42">
+        <v>0.38821499999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D43">
+        <v>0.01</v>
+      </c>
+      <c r="E43">
+        <v>0.12523799999999999</v>
+      </c>
+      <c r="F43">
+        <v>0.36</v>
+      </c>
+      <c r="L43">
+        <v>5.6820000000000004E-3</v>
+      </c>
+      <c r="M43">
+        <v>0.12786800000000001</v>
+      </c>
+      <c r="N43">
+        <v>0.38977299999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="5" t="s">
+      <c r="C44" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D44">
+        <v>4.2370000000000003E-3</v>
+      </c>
+      <c r="E44">
+        <v>0.12711900000000001</v>
+      </c>
+      <c r="F44">
+        <v>0.37711899999999998</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0.110571</v>
+      </c>
+      <c r="N44">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" t="s">
         <v>167</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="6">
-        <v>236</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>0.120056</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="C45" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D45">
+        <v>2.398E-3</v>
+      </c>
+      <c r="E45">
+        <v>0.126413</v>
+      </c>
+      <c r="F45">
+        <v>0.38369300000000001</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0.114286</v>
+      </c>
+      <c r="N45">
+        <v>0.58050800000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D46">
+        <v>1.7329999999999999E-3</v>
+      </c>
+      <c r="E46">
+        <v>0.12742400000000001</v>
+      </c>
+      <c r="F46">
+        <v>0.38821499999999998</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0.116273</v>
+      </c>
+      <c r="N46">
+        <v>0.61870499999999995</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D47">
+        <v>5.6820000000000004E-3</v>
+      </c>
+      <c r="E47">
+        <v>0.12786800000000001</v>
+      </c>
+      <c r="F47">
+        <v>0.38977299999999998</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0.116316</v>
+      </c>
+      <c r="N47">
+        <v>0.62565000000000004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0.110571</v>
+      </c>
+      <c r="F48">
+        <v>0.51</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0.117175</v>
+      </c>
+      <c r="N48">
+        <v>0.63636400000000004</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="J16">
-        <v>1.6948999999999999E-2</v>
-      </c>
-      <c r="K16">
-        <v>0.67796599999999996</v>
-      </c>
-      <c r="L16">
-        <v>12.005649999999999</v>
-      </c>
-      <c r="M16" t="s">
-        <v>166</v>
-      </c>
-      <c r="N16">
-        <v>1.6949149999999999</v>
-      </c>
-      <c r="O16">
-        <v>67.796610000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D17" t="s">
+      <c r="C49" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0.114286</v>
+      </c>
+      <c r="F49">
+        <v>0.58050800000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>164</v>
+      </c>
+      <c r="B50" t="s">
+        <v>167</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0.116273</v>
+      </c>
+      <c r="F50">
+        <v>0.61870499999999995</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>164</v>
+      </c>
+      <c r="B51" t="s">
         <v>168</v>
       </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17">
-        <v>417</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>0.120132</v>
-      </c>
-      <c r="I17" t="s">
-        <v>166</v>
-      </c>
-      <c r="J17">
-        <v>9.5919999999999998E-3</v>
-      </c>
-      <c r="K17">
-        <v>0.81774599999999997</v>
-      </c>
-      <c r="L17">
-        <v>12.013247</v>
-      </c>
-      <c r="M17" t="s">
-        <v>166</v>
-      </c>
-      <c r="N17">
-        <v>0.959233</v>
-      </c>
-      <c r="O17">
-        <v>81.77458</v>
-      </c>
-    </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D18" t="s">
+      <c r="C51" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0.116316</v>
+      </c>
+      <c r="F51">
+        <v>0.62565000000000004</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" t="s">
         <v>169</v>
       </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18">
-        <v>577</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>0.120409</v>
-      </c>
-      <c r="I18" t="s">
-        <v>166</v>
-      </c>
-      <c r="J18">
-        <v>6.9319999999999998E-3</v>
-      </c>
-      <c r="K18">
-        <v>0.86828399999999994</v>
-      </c>
-      <c r="L18">
-        <v>12.040934</v>
-      </c>
-      <c r="M18" t="s">
-        <v>166</v>
-      </c>
-      <c r="N18">
-        <v>0.693241</v>
-      </c>
-      <c r="O18">
-        <v>86.828423000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19">
-        <v>880</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>0.120292</v>
-      </c>
-      <c r="I19" t="s">
-        <v>166</v>
-      </c>
-      <c r="J19">
-        <v>2.2729999999999998E-3</v>
-      </c>
-      <c r="K19">
-        <v>0.92613599999999996</v>
-      </c>
-      <c r="L19">
-        <v>12.029221</v>
-      </c>
-      <c r="M19" t="s">
-        <v>166</v>
-      </c>
-      <c r="N19">
-        <v>0.227273</v>
-      </c>
-      <c r="O19">
-        <v>92.613636</v>
+      <c r="C52" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0.117175</v>
+      </c>
+      <c r="F52">
+        <v>0.63636400000000004</v>
       </c>
     </row>
   </sheetData>
@@ -4151,18 +6611,1623 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C41AEE1E-4CBB-415F-95F8-165D4B6A1E64}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2">
+        <f>D2/J2</f>
+        <v>80.441950552161103</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J2">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E52" si="0">D3/J3</f>
+        <v>71.365125978740068</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J3">
+        <v>10.176</v>
+      </c>
+      <c r="L3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>67.421973570460977</v>
+      </c>
+      <c r="I4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J4">
+        <v>17.376000000000001</v>
+      </c>
+      <c r="L4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>50.667970936754053</v>
+      </c>
+      <c r="I5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J5">
+        <v>25.632000000000001</v>
+      </c>
+      <c r="L5" t="s">
+        <v>317</v>
+      </c>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>52.547570715546932</v>
+      </c>
+      <c r="I6" t="s">
+        <v>169</v>
+      </c>
+      <c r="J6">
+        <v>42.143999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>44.595572843201843</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J7">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>42.965354449055326</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J8">
+        <v>10.176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>41.470394086975773</v>
+      </c>
+      <c r="I9" t="s">
+        <v>167</v>
+      </c>
+      <c r="J9">
+        <v>17.376000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>38.471345268472767</v>
+      </c>
+      <c r="I10" t="s">
+        <v>168</v>
+      </c>
+      <c r="J10">
+        <v>25.632000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>33.174829856155327</v>
+      </c>
+      <c r="I11" t="s">
+        <v>169</v>
+      </c>
+      <c r="J11">
+        <v>42.143999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>62.246433339000234</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J12">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>58.704390732888555</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J13">
+        <v>10.176</v>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="5">
+        <v>930.32692783878394</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>53.540914355362794</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" t="s">
+        <v>167</v>
+      </c>
+      <c r="J14">
+        <v>17.376000000000001</v>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>48.583990871523874</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" t="s">
+        <v>168</v>
+      </c>
+      <c r="J15">
+        <v>25.632000000000001</v>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>39.05733613726391</v>
+      </c>
+      <c r="I16" t="s">
+        <v>169</v>
+      </c>
+      <c r="J16">
+        <v>42.143999999999998</v>
+      </c>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>81.406176882568502</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J17">
+        <v>4.32</v>
+      </c>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>75.107614330049429</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J18">
+        <v>10.176</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="6"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>73.067141622036701</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" t="s">
+        <v>167</v>
+      </c>
+      <c r="J19">
+        <v>17.376000000000001</v>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="6"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>66.909506141251555</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" t="s">
+        <v>168</v>
+      </c>
+      <c r="J20">
+        <v>25.632000000000001</v>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>57.893484637367123</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" t="s">
+        <v>169</v>
+      </c>
+      <c r="J21">
+        <v>42.143999999999998</v>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="6"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22">
+        <v>432.41559999999998</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>100.09620370370369</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J22">
+        <v>4.32</v>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>949.4769</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>93.305512971698107</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J23">
+        <v>10.176</v>
+      </c>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24">
+        <v>1576.2992999999999</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>90.717040745856337</v>
+      </c>
+      <c r="I24" t="s">
+        <v>167</v>
+      </c>
+      <c r="J24">
+        <v>17.376000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>2192.8779</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>85.552352528089884</v>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" t="s">
+        <v>168</v>
+      </c>
+      <c r="J25">
+        <v>25.632000000000001</v>
+      </c>
+      <c r="K25" s="6"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26">
+        <v>3317.6731</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>78.72231159832954</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26">
+        <v>42.143999999999998</v>
+      </c>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="0"/>
+        <v>87.804579426334953</v>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J28">
+        <v>4.32</v>
+      </c>
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="0"/>
+        <v>82.870028218390928</v>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J29">
+        <v>10.176</v>
+      </c>
+      <c r="K29" s="6"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="0"/>
+        <v>74.131137549290386</v>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" t="s">
+        <v>167</v>
+      </c>
+      <c r="J30">
+        <v>17.376000000000001</v>
+      </c>
+      <c r="K30" s="6"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="0"/>
+        <v>64.281720582878435</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" t="s">
+        <v>168</v>
+      </c>
+      <c r="J31">
+        <v>25.632000000000001</v>
+      </c>
+      <c r="K31" s="6"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="0"/>
+        <v>52.619272841946668</v>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" t="s">
+        <v>169</v>
+      </c>
+      <c r="J32">
+        <v>42.143999999999998</v>
+      </c>
+      <c r="K32" s="6"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="0"/>
+        <v>43.092501103842821</v>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33">
+        <v>4.32</v>
+      </c>
+      <c r="K33" s="6"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="0"/>
+        <v>41.468475240803748</v>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J34">
+        <v>10.176</v>
+      </c>
+      <c r="K34" s="6"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="0"/>
+        <v>40.23390105181474</v>
+      </c>
+      <c r="I35" t="s">
+        <v>167</v>
+      </c>
+      <c r="J35">
+        <v>17.376000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="0"/>
+        <v>36.639639445892129</v>
+      </c>
+      <c r="I36" t="s">
+        <v>168</v>
+      </c>
+      <c r="J36">
+        <v>25.632000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>169</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="0"/>
+        <v>31.05140677230472</v>
+      </c>
+      <c r="I37" t="s">
+        <v>169</v>
+      </c>
+      <c r="J37">
+        <v>42.143999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="0"/>
+        <v>58.764601563095368</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J38">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="0"/>
+        <v>55.886791533863992</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J39">
+        <v>10.176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>167</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="0"/>
+        <v>51.837280636112219</v>
+      </c>
+      <c r="I40" t="s">
+        <v>167</v>
+      </c>
+      <c r="J40">
+        <v>17.376000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>168</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="0"/>
+        <v>46.568328151763026</v>
+      </c>
+      <c r="I41" t="s">
+        <v>168</v>
+      </c>
+      <c r="J41">
+        <v>25.632000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="0"/>
+        <v>36.943621635691201</v>
+      </c>
+      <c r="I42" t="s">
+        <v>169</v>
+      </c>
+      <c r="J42">
+        <v>42.143999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="0"/>
+        <v>81.15205881193819</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J43">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="0"/>
+        <v>76.324582662645739</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J44">
+        <v>10.176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="0"/>
+        <v>72.049280192692223</v>
+      </c>
+      <c r="I45" t="s">
+        <v>167</v>
+      </c>
+      <c r="J45">
+        <v>17.376000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="0"/>
+        <v>66.292272977924853</v>
+      </c>
+      <c r="I46" t="s">
+        <v>168</v>
+      </c>
+      <c r="J46">
+        <v>25.632000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="0"/>
+        <v>56.551254038762337</v>
+      </c>
+      <c r="I47" t="s">
+        <v>169</v>
+      </c>
+      <c r="J47">
+        <v>42.143999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D48">
+        <v>388.02140000000003</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="0"/>
+        <v>89.819768518518515</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="J48">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D49">
+        <v>876.76229999999998</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="0"/>
+        <v>86.159817216981125</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J49">
+        <v>10.176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>164</v>
+      </c>
+      <c r="B50" t="s">
+        <v>167</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D50">
+        <v>1459.4879000000001</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="0"/>
+        <v>83.994469383057094</v>
+      </c>
+      <c r="I50" t="s">
+        <v>167</v>
+      </c>
+      <c r="J50">
+        <v>17.376000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>164</v>
+      </c>
+      <c r="B51" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D51">
+        <v>2022.8336999999999</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="0"/>
+        <v>78.91829353932583</v>
+      </c>
+      <c r="I51" t="s">
+        <v>168</v>
+      </c>
+      <c r="J51">
+        <v>25.632000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D52">
+        <v>3090.5210999999999</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="0"/>
+        <v>73.33241030751708</v>
+      </c>
+      <c r="I52" t="s">
+        <v>169</v>
+      </c>
+      <c r="J52">
+        <v>42.143999999999998</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F8AFFA-BDF2-4CED-A1EC-52A1037ECE42}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B2">
+        <v>344</v>
+      </c>
+      <c r="C2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3">
+        <v>172</v>
+      </c>
+      <c r="C3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4">
+        <v>150</v>
+      </c>
+      <c r="C4" t="s">
+        <v>305</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>306</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="K5" s="10">
+        <v>13</v>
+      </c>
+      <c r="L5" s="10">
+        <v>6</v>
+      </c>
+      <c r="M5" s="10">
+        <v>22</v>
+      </c>
+      <c r="N5" s="10">
+        <v>14</v>
+      </c>
+      <c r="O5" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6">
+        <v>122</v>
+      </c>
+      <c r="C6" t="s">
+        <v>308</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="K6" s="10">
+        <v>23</v>
+      </c>
+      <c r="L6" s="10">
+        <v>8</v>
+      </c>
+      <c r="M6" s="10">
+        <v>35</v>
+      </c>
+      <c r="N6" s="10">
+        <v>23</v>
+      </c>
+      <c r="O6" s="10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="23.5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7">
+        <v>212</v>
+      </c>
+      <c r="C7" t="s">
+        <v>309</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="L7" s="11">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="M7" s="12">
+        <v>0.152</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0.253</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0.24199999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8">
+        <v>362</v>
+      </c>
+      <c r="C8" t="s">
+        <v>310</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="K8" s="11">
+        <v>14.6</v>
+      </c>
+      <c r="L8" s="10">
+        <v>240</v>
+      </c>
+      <c r="M8" s="10">
+        <v>147</v>
+      </c>
+      <c r="N8" s="10">
+        <v>233</v>
+      </c>
+      <c r="O8" s="12">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="36" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9">
+        <v>534</v>
+      </c>
+      <c r="C9" t="s">
+        <v>311</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="K9" s="11">
+        <v>30</v>
+      </c>
+      <c r="L9" s="10">
+        <v>368</v>
+      </c>
+      <c r="M9" s="10">
+        <v>385</v>
+      </c>
+      <c r="N9" s="10">
+        <v>505</v>
+      </c>
+      <c r="O9" s="12">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="24.5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10">
+        <v>878</v>
+      </c>
+      <c r="C10" t="s">
+        <v>312</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="K10" s="11">
+        <v>78</v>
+      </c>
+      <c r="L10" s="10">
+        <v>720</v>
+      </c>
+      <c r="M10" s="10">
+        <v>948</v>
+      </c>
+      <c r="N10" s="10">
+        <v>1040</v>
+      </c>
+      <c r="O10" s="12">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="35" x14ac:dyDescent="0.25">
+      <c r="J11" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.21</v>
+      </c>
+      <c r="L11" s="11">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="M11" s="12">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="O11" s="10">
+        <v>0.25900000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>